--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92571854617</v>
+        <v>46157.93110196064</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93110196064</v>
+        <v>46157.93178647864</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93178647864</v>
+        <v>46157.93403447295</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93403447295</v>
+        <v>46157.9372143961</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9372143961</v>
+        <v>46158.28219428907</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28219428907</v>
+        <v>46158.29694235903</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29694235903</v>
+        <v>46158.298188491</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.298188491</v>
+        <v>46158.33390512222</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33390512222</v>
+        <v>46158.36860251991</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/36. ИП Рыбалко/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36860251991</v>
+        <v>46158.37290952422</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
